--- a/pricing/商务成品/对外/定制报价/Trinity模型报价表_hehe.xlsx
+++ b/pricing/商务成品/对外/定制报价/Trinity模型报价表_hehe.xlsx
@@ -6,7 +6,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29400" windowHeight="14120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仅有折扣" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仅有折扣" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -16,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="28">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -196,6 +197,22 @@
       <name val="宋体-简"/>
       <charset val="134"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="00713F12"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="001D2939"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="40">
@@ -433,7 +450,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -596,6 +613,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D5DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D5DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D5DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D5DD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -744,7 +775,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -801,6 +832,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="3" applyFill="1" applyBorder="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyFill="1" applyFont="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="14" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1213,6 +1256,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>本页为 hehe 定制表累积更新日志（新→旧），供 Trinity 对内核对；外发客户前可删本页。重建/同步：pricing/scripts/sync_hehe_discount_models.py。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>更新说明</t>
+        </is>
+      </c>
+      <c r="D2" s="27" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>2026.9.20</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>hehe</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>启用「更新」累积日志；本轮无同步变更</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>定制表 · 首启</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
@@ -2748,7 +2865,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="n"/>
+      <c r="A46" s="6" t="n"/>
       <c r="B46" s="22" t="n"/>
       <c r="C46" s="23" t="inlineStr">
         <is>
@@ -2918,8 +3035,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="n"/>
-      <c r="B51" s="22" t="n"/>
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="6" t="n"/>
       <c r="C51" s="23" t="inlineStr">
         <is>
           <t>deepseek-v4-flash</t>
@@ -2952,8 +3069,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="n"/>
-      <c r="B52" s="22" t="n"/>
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="6" t="n"/>
       <c r="C52" s="23" t="inlineStr">
         <is>
           <t>deepseek-v4-pro</t>
@@ -3224,7 +3341,7 @@
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="22" t="n"/>
+      <c r="A60" s="6" t="n"/>
       <c r="B60" s="25" t="n"/>
       <c r="C60" s="23" t="inlineStr">
         <is>
